--- a/output/pdf_financials_xlsx/AGMR.xlsx
+++ b/output/pdf_financials_xlsx/AGMR.xlsx
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.020792</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.097637</v>
       </c>
     </row>
     <row r="13">
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.11119</v>
+        <v>-2.131982</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-35.456836</v>
+        <v>-35.554473</v>
       </c>
     </row>
     <row r="28">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.105621</v>
+        <v>-2.126413</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-35.436798</v>
+        <v>-35.534435</v>
       </c>
     </row>
     <row r="30">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0055</v>
       </c>
     </row>
     <row r="125">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0055</v>
       </c>
     </row>
     <row r="126">
@@ -9542,7 +9542,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -13706,7 +13710,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">

--- a/output/pdf_financials_xlsx/AGMR.xlsx
+++ b/output/pdf_financials_xlsx/AGMR.xlsx
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -12142,7 +12142,11 @@
           <t>Proceeds from disposal of property, plant, and equipment</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AGMR.xlsx
+++ b/output/pdf_financials_xlsx/AGMR.xlsx
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.524125</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.584606</v>
       </c>
     </row>
     <row r="65">
@@ -2320,10 +2320,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.09113300000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>2.601756</v>
       </c>
     </row>
     <row r="68">
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.136655</v>
       </c>
     </row>
     <row r="111">
@@ -8596,7 +8596,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
